--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf23cf1af8306441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd5423852d8a49b4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd5423852d8a49b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62f5f5011d4e4264"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62f5f5011d4e4264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R218e8141ba7f40d5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R218e8141ba7f40d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0eede39ce3d54274"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0eede39ce3d54274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28b8faeeee734b84"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28b8faeeee734b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8cd9788b644040b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8cd9788b644040b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R373060c793914aba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R373060c793914aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb52d218319ba493a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb52d218319ba493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1656faca5fcf4ba2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1656faca5fcf4ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R862b7a910921495f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R862b7a910921495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R109d31013bff4f3d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R109d31013bff4f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83b8b1331f1b477f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83b8b1331f1b477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R165d17ad1b264cca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R165d17ad1b264cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R70bb9f2b8d254984"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R70bb9f2b8d254984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re438889c4d0c4cba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re438889c4d0c4cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8196a3ff87004d46"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8196a3ff87004d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf979ebdd40f04da9"/>
   </x:sheets>
 </x:workbook>
 </file>
